--- a/Série histórica das medições - Grupo DPJ.xlsx
+++ b/Série histórica das medições - Grupo DPJ.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Painel Streamlit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.pereira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D03C17B-E858-4476-96C2-E405965C29D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Pessoa</t>
   </si>
@@ -86,12 +85,15 @@
   </si>
   <si>
     <t>Meta</t>
+  </si>
+  <si>
+    <t>Igor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -148,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -160,6 +162,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,8 +464,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -865,7 +868,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="6">
-        <v>46144</v>
+        <v>46058</v>
       </c>
       <c r="C14" s="5">
         <v>88.1</v>
@@ -889,6 +892,36 @@
         <v>8</v>
       </c>
       <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46071</v>
+      </c>
+      <c r="C15" s="7">
+        <v>86.2</v>
+      </c>
+      <c r="D15" s="7">
+        <v>25.7</v>
+      </c>
+      <c r="E15" s="7">
+        <v>26.4</v>
+      </c>
+      <c r="F15" s="7">
+        <v>34</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1797</v>
+      </c>
+      <c r="H15" s="7">
+        <v>57</v>
+      </c>
+      <c r="I15" s="7">
+        <v>9</v>
+      </c>
+      <c r="J15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Série histórica das medições - Grupo DPJ.xlsx
+++ b/Série histórica das medições - Grupo DPJ.xlsx
@@ -9,17 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11880"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="4260" windowHeight="9960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$27</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Pessoa</t>
   </si>
@@ -115,12 +118,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -150,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -163,6 +172,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,13 +477,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +516,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -535,7 +548,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -560,10 +573,12 @@
       <c r="H3" s="3">
         <v>63</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>9</v>
+      </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -592,8 +607,9 @@
         <v>14</v>
       </c>
       <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -623,7 +639,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -653,7 +669,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -683,7 +699,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -713,7 +729,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -743,7 +759,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -773,7 +789,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -803,127 +819,285 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6">
+        <v>46055</v>
+      </c>
+      <c r="C12" s="5">
+        <v>71.2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>23.5</v>
+      </c>
+      <c r="E12" s="5">
+        <v>22</v>
+      </c>
+      <c r="F12" s="5">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1613</v>
+      </c>
+      <c r="H12" s="5">
+        <v>40</v>
+      </c>
+      <c r="I12" s="5">
+        <v>7</v>
+      </c>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="6">
+        <v>46058</v>
+      </c>
+      <c r="C13" s="5">
+        <v>88.1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>30.4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>47.2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1606</v>
+      </c>
+      <c r="H13" s="5">
+        <v>54</v>
+      </c>
+      <c r="I13" s="5">
+        <v>8</v>
+      </c>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46071</v>
+      </c>
+      <c r="C14" s="7">
+        <v>86.2</v>
+      </c>
+      <c r="D14" s="7">
+        <v>25.7</v>
+      </c>
+      <c r="E14" s="7">
+        <v>26.4</v>
+      </c>
+      <c r="F14" s="7">
+        <v>34</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1797</v>
+      </c>
+      <c r="H14" s="7">
+        <v>57</v>
+      </c>
+      <c r="I14" s="7">
+        <v>9</v>
+      </c>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
-        <v>46052</v>
-      </c>
-      <c r="C12" s="3">
-        <v>83.9</v>
-      </c>
-      <c r="D12" s="3">
-        <v>28.7</v>
-      </c>
-      <c r="E12" s="3">
-        <v>30.2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>33.6</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1818</v>
-      </c>
-      <c r="H12" s="3">
-        <v>53</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="B15" s="10">
+        <v>46083</v>
+      </c>
+      <c r="C15" s="9">
+        <v>84.2</v>
+      </c>
+      <c r="D15" s="9">
+        <v>29.3</v>
+      </c>
+      <c r="E15" s="9">
+        <v>27.5</v>
+      </c>
+      <c r="F15" s="9">
+        <v>35</v>
+      </c>
+      <c r="G15" s="9">
+        <v>1815</v>
+      </c>
+      <c r="H15" s="9">
+        <v>52</v>
+      </c>
+      <c r="I15" s="9">
+        <v>12</v>
+      </c>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46083</v>
+      </c>
+      <c r="C16" s="9">
+        <v>95</v>
+      </c>
+      <c r="D16" s="9">
+        <v>29.3</v>
+      </c>
+      <c r="E16" s="9">
+        <v>29.3</v>
+      </c>
+      <c r="F16" s="9">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1919</v>
+      </c>
+      <c r="H16" s="9">
+        <v>65</v>
+      </c>
+      <c r="I16" s="9">
         <v>13</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="6">
-        <v>46055</v>
-      </c>
-      <c r="C13" s="5">
-        <v>71.2</v>
-      </c>
-      <c r="D13" s="5">
-        <v>23.5</v>
-      </c>
-      <c r="E13" s="5">
-        <v>22</v>
-      </c>
-      <c r="F13" s="5">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="G13" s="5">
-        <v>1613</v>
-      </c>
-      <c r="H13" s="5">
-        <v>40</v>
-      </c>
-      <c r="I13" s="5">
-        <v>7</v>
-      </c>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="6">
-        <v>46058</v>
-      </c>
-      <c r="C14" s="5">
-        <v>88.1</v>
-      </c>
-      <c r="D14" s="5">
-        <v>30.4</v>
-      </c>
-      <c r="E14" s="5">
-        <v>47.2</v>
-      </c>
-      <c r="F14" s="5">
-        <v>22.6</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1606</v>
-      </c>
-      <c r="H14" s="5">
-        <v>54</v>
-      </c>
-      <c r="I14" s="5">
-        <v>8</v>
-      </c>
-      <c r="J14" s="5"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="4">
-        <v>46071</v>
-      </c>
-      <c r="C15" s="7">
-        <v>86.2</v>
-      </c>
-      <c r="D15" s="7">
-        <v>25.7</v>
-      </c>
-      <c r="E15" s="7">
-        <v>26.4</v>
-      </c>
-      <c r="F15" s="7">
-        <v>34</v>
-      </c>
-      <c r="G15" s="7">
-        <v>1797</v>
-      </c>
-      <c r="H15" s="7">
-        <v>57</v>
-      </c>
-      <c r="I15" s="7">
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46083</v>
+      </c>
+      <c r="C17" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="D17" s="9">
+        <v>24.8</v>
+      </c>
+      <c r="E17" s="9">
+        <v>21.4</v>
+      </c>
+      <c r="F17" s="9">
+        <v>38.9</v>
+      </c>
+      <c r="G17" s="9">
+        <v>1882</v>
+      </c>
+      <c r="H17" s="9">
+        <v>47</v>
+      </c>
+      <c r="I17" s="9">
+        <v>6</v>
+      </c>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46083</v>
+      </c>
+      <c r="C18" s="9">
+        <v>55.6</v>
+      </c>
+      <c r="D18" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E18" s="9">
+        <v>28.9</v>
+      </c>
+      <c r="F18" s="9">
+        <v>28.2</v>
+      </c>
+      <c r="G18" s="9">
+        <v>1282</v>
+      </c>
+      <c r="H18" s="9">
+        <v>18</v>
+      </c>
+      <c r="I18" s="9">
+        <v>3</v>
+      </c>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
+      <c r="B19" s="10">
+        <v>46083</v>
+      </c>
+      <c r="C19" s="9">
+        <v>75.7</v>
+      </c>
+      <c r="D19" s="9">
+        <v>34.1</v>
+      </c>
+      <c r="E19" s="9">
+        <v>50.7</v>
+      </c>
+      <c r="F19" s="9">
+        <v>21.3</v>
+      </c>
+      <c r="G19" s="9">
+        <v>1371</v>
+      </c>
+      <c r="H19" s="9">
+        <v>63</v>
+      </c>
+      <c r="I19" s="9">
+        <v>9</v>
+      </c>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46083</v>
+      </c>
+      <c r="C20" s="9">
+        <v>81.3</v>
+      </c>
+      <c r="D20" s="9">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E20" s="9">
+        <v>46.5</v>
+      </c>
+      <c r="F20" s="9">
+        <v>23.3</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1497</v>
+      </c>
+      <c r="H20" s="9">
+        <v>69</v>
+      </c>
+      <c r="I20" s="9">
+        <v>11</v>
+      </c>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="A1:J27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Série histórica das medições - Grupo DPJ.xlsx
+++ b/Série histórica das medições - Grupo DPJ.xlsx
@@ -1,11 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73400296-65C3-4BE4-8FF2-941E9B64480F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.pereira\Downloads\v03032026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10980"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -13,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$21</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>Pessoa</t>
   </si>
@@ -105,83 +109,14 @@
     <t>Igor</t>
   </si>
   <si>
-    <t>86,2</t>
-  </si>
-  <si>
-    <t>25,7</t>
-  </si>
-  <si>
-    <t>26,4</t>
-  </si>
-  <si>
     <t> </t>
-  </si>
-  <si>
-    <t>84,2</t>
-  </si>
-  <si>
-    <t>29,3</t>
-  </si>
-  <si>
-    <t>27,5</t>
-  </si>
-  <si>
-    <t>32,7</t>
-  </si>
-  <si>
-    <t>87,5</t>
-  </si>
-  <si>
-    <t>24,8</t>
-  </si>
-  <si>
-    <t>21,4</t>
-  </si>
-  <si>
-    <t>38,9</t>
-  </si>
-  <si>
-    <t>55,6</t>
-  </si>
-  <si>
-    <t>19,9</t>
-  </si>
-  <si>
-    <t>28,9</t>
-  </si>
-  <si>
-    <t>28,2</t>
-  </si>
-  <si>
-    <t>75,7</t>
-  </si>
-  <si>
-    <t>34,1</t>
-  </si>
-  <si>
-    <t>50,7</t>
-  </si>
-  <si>
-    <t>21,3</t>
-  </si>
-  <si>
-    <t>81,3</t>
-  </si>
-  <si>
-    <t>32,2</t>
-  </si>
-  <si>
-    <t>46,5</t>
-  </si>
-  <si>
-    <t>23,3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,16 +265,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -655,19 +590,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="13"/>
+    <col min="3" max="3" width="9.140625" style="11"/>
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +666,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -761,7 +696,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -791,7 +726,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -821,7 +756,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -851,7 +786,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -881,7 +816,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -911,7 +846,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -941,7 +876,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -971,7 +906,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -1001,7 +936,7 @@
       </c>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1031,7 +966,7 @@
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1061,23 +996,23 @@
       </c>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>46071</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="11">
+      <c r="C14" s="13">
+        <v>86.2</v>
+      </c>
+      <c r="D14" s="13">
+        <v>25.7</v>
+      </c>
+      <c r="E14" s="13">
+        <v>26.4</v>
+      </c>
+      <c r="F14" s="13">
         <v>34</v>
       </c>
       <c r="G14" s="8">
@@ -1090,26 +1025,26 @@
         <v>9</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="12">
         <v>46056</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="12">
+      <c r="C15" s="14">
+        <v>84.2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>29.3</v>
+      </c>
+      <c r="E15" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="F15" s="14">
         <v>35</v>
       </c>
       <c r="G15" s="5">
@@ -1122,27 +1057,27 @@
         <v>12</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="12">
         <v>46056</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="14">
         <v>95</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>30</v>
+      <c r="D16" s="14">
+        <v>29.3</v>
+      </c>
+      <c r="E16" s="14">
+        <v>29.3</v>
+      </c>
+      <c r="F16" s="14">
+        <v>32.700000000000003</v>
       </c>
       <c r="G16" s="5">
         <v>1919</v>
@@ -1154,27 +1089,27 @@
         <v>13</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="12">
         <v>46056</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>34</v>
+      <c r="C17" s="14">
+        <v>87.5</v>
+      </c>
+      <c r="D17" s="14">
+        <v>24.8</v>
+      </c>
+      <c r="E17" s="14">
+        <v>21.4</v>
+      </c>
+      <c r="F17" s="14">
+        <v>38.9</v>
       </c>
       <c r="G17" s="5">
         <v>1882</v>
@@ -1186,27 +1121,27 @@
         <v>6</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <v>46056</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>38</v>
+      <c r="C18" s="14">
+        <v>55.6</v>
+      </c>
+      <c r="D18" s="14">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E18" s="14">
+        <v>28.9</v>
+      </c>
+      <c r="F18" s="14">
+        <v>28.2</v>
       </c>
       <c r="G18" s="5">
         <v>1282</v>
@@ -1218,27 +1153,27 @@
         <v>3</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="12">
         <v>46056</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>42</v>
+      <c r="C19" s="14">
+        <v>75.7</v>
+      </c>
+      <c r="D19" s="14">
+        <v>34.1</v>
+      </c>
+      <c r="E19" s="14">
+        <v>50.7</v>
+      </c>
+      <c r="F19" s="14">
+        <v>21.3</v>
       </c>
       <c r="G19" s="5">
         <v>1371</v>
@@ -1250,27 +1185,27 @@
         <v>9</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="12">
         <v>46056</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>46</v>
+      <c r="C20" s="14">
+        <v>81.3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E20" s="14">
+        <v>46.5</v>
+      </c>
+      <c r="F20" s="14">
+        <v>23.3</v>
       </c>
       <c r="G20" s="5">
         <v>1497</v>
@@ -1282,26 +1217,26 @@
         <v>11</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="12">
         <v>46056</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="14">
         <v>71</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="14">
         <v>25.2</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="14">
         <v>24.9</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="14">
         <v>37.700000000000003</v>
       </c>
       <c r="G21" s="5">
@@ -1315,8 +1250,11 @@
       </c>
       <c r="J21" s="5"/>
     </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D22" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Série histórica das medições - Grupo DPJ.xlsx
+++ b/Série histórica das medições - Grupo DPJ.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Pessoa</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t> </t>
+  </si>
+  <si>
+    <t>Gabriela</t>
   </si>
 </sst>
 </file>
@@ -159,27 +162,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -197,84 +185,33 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -591,11 +528,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="11"/>
+    <col min="3" max="3" width="9.140625" style="4"/>
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
@@ -609,7 +546,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -635,396 +572,396 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>46048</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="6">
         <v>84.9</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="6">
         <v>29.4</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="6">
         <v>30.4</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="6">
         <v>33.1</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="9">
         <v>1818</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="9">
         <v>53</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="9">
         <v>13</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="9">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
         <v>46048</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="6">
         <v>75.7</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="6">
         <v>34.1</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="6">
         <v>50.9</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="9">
         <v>1371</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="9">
         <v>63</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="9">
         <v>9</v>
       </c>
-      <c r="J3" s="2"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>46048</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <v>100.4</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="6">
         <v>31</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="6">
         <v>32.5</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="6">
         <v>30.9</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="9">
         <v>1986</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="9">
         <v>70</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="9">
         <v>14</v>
       </c>
-      <c r="J4" s="2"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>46048</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <v>86.4</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="6">
         <v>24.4</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="6">
         <v>22.8</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="6">
         <v>38.799999999999997</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="9">
         <v>1862</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="9">
         <v>46</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="9">
         <v>6</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>46048</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <v>64.400000000000006</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="6">
         <v>25.8</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="6">
         <v>38.5</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="6">
         <v>26.5</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="9">
         <v>1311</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="9">
         <v>37</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="9">
         <v>5</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>46048</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="6">
         <v>61.1</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="6">
         <v>22.4</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="6">
         <v>35.5</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="6">
         <v>26</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="9">
         <v>1317</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="9">
         <v>24</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="9">
         <v>4</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>46048</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="6">
         <v>56.3</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="6">
         <v>20.3</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="6">
         <v>29.4</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="6">
         <v>28.2</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="9">
         <v>1288</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="9">
         <v>20</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="9">
         <v>3</v>
       </c>
-      <c r="J8" s="2"/>
+      <c r="J8" s="9"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>46048</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="6">
         <v>62.4</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="6">
         <v>23.2</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="6">
         <v>37.4</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="6">
         <v>24.8</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="9">
         <v>1331</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="9">
         <v>38</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="9">
         <v>5</v>
       </c>
-      <c r="J9" s="2"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>46049</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="6">
         <v>81.5</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="6">
         <v>31.8</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="6">
         <v>49.1</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="6">
         <v>21.4</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="9">
         <v>1492</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="9">
         <v>69</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="9">
         <v>11</v>
       </c>
-      <c r="J10" s="2"/>
+      <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>46049</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="6">
         <v>72</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="6">
         <v>25.5</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="6">
         <v>24.3</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="6">
         <v>38.299999999999997</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="9">
         <v>1687</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="9">
         <v>33</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="9">
         <v>8</v>
       </c>
-      <c r="J11" s="2"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>46055</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="6">
         <v>71.2</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="6">
         <v>23.5</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="6">
         <v>22</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="6">
         <v>36.799999999999997</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="9">
         <v>1613</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="9">
         <v>40</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="9">
         <v>7</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>46058</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="6">
         <v>88.1</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="6">
         <v>30.4</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="6">
         <v>47.2</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="6">
         <v>22.6</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="9">
         <v>1606</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="9">
         <v>54</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="9">
         <v>8</v>
       </c>
-      <c r="J13" s="2"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="2">
         <v>46071</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="7">
         <v>86.2</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="7">
         <v>25.7</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="7">
         <v>26.4</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="7">
         <v>34</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="10">
         <v>1797</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="10">
         <v>57</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="10">
         <v>9</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="10" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1032,19 +969,19 @@
       <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="12">
-        <v>46056</v>
-      </c>
-      <c r="C15" s="14">
+      <c r="B15" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C15" s="8">
         <v>84.2</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="8">
         <v>29.3</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="8">
         <v>27.5</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="8">
         <v>35</v>
       </c>
       <c r="G15" s="5">
@@ -1064,19 +1001,19 @@
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="12">
-        <v>46056</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="B16" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C16" s="8">
         <v>95</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="8">
         <v>29.3</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="8">
         <v>29.3</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="8">
         <v>32.700000000000003</v>
       </c>
       <c r="G16" s="5">
@@ -1096,19 +1033,19 @@
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="12">
-        <v>46056</v>
-      </c>
-      <c r="C17" s="14">
+      <c r="B17" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C17" s="8">
         <v>87.5</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="8">
         <v>24.8</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="8">
         <v>21.4</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="8">
         <v>38.9</v>
       </c>
       <c r="G17" s="5">
@@ -1128,19 +1065,19 @@
       <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="12">
-        <v>46056</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C18" s="8">
         <v>55.6</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="8">
         <v>19.899999999999999</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="8">
         <v>28.9</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="8">
         <v>28.2</v>
       </c>
       <c r="G18" s="5">
@@ -1160,19 +1097,19 @@
       <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="12">
-        <v>46056</v>
-      </c>
-      <c r="C19" s="14">
+      <c r="B19" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C19" s="8">
         <v>75.7</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="8">
         <v>34.1</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="8">
         <v>50.7</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="8">
         <v>21.3</v>
       </c>
       <c r="G19" s="5">
@@ -1192,19 +1129,19 @@
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="12">
-        <v>46056</v>
-      </c>
-      <c r="C20" s="14">
+      <c r="B20" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C20" s="8">
         <v>81.3</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="8">
         <v>32.200000000000003</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="8">
         <v>46.5</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="8">
         <v>23.3</v>
       </c>
       <c r="G20" s="5">
@@ -1224,19 +1161,19 @@
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="12">
-        <v>46056</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="B21" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C21" s="8">
         <v>71</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="8">
         <v>25.2</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="8">
         <v>24.9</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="8">
         <v>37.700000000000003</v>
       </c>
       <c r="G21" s="5">
@@ -1251,7 +1188,64 @@
       <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D22" s="13"/>
+      <c r="A22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C22" s="8">
+        <v>63.3</v>
+      </c>
+      <c r="D22" s="8">
+        <v>23.5</v>
+      </c>
+      <c r="E22" s="8">
+        <v>38.4</v>
+      </c>
+      <c r="F22" s="8">
+        <v>24.3</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1340</v>
+      </c>
+      <c r="H22" s="5">
+        <v>38</v>
+      </c>
+      <c r="I22" s="5">
+        <v>6</v>
+      </c>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C23" s="8">
+        <v>53.8</v>
+      </c>
+      <c r="D23" s="8">
+        <v>23.3</v>
+      </c>
+      <c r="E23" s="8">
+        <v>30.7</v>
+      </c>
+      <c r="F23" s="8">
+        <v>29.8</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1193</v>
+      </c>
+      <c r="H23" s="5">
+        <v>47</v>
+      </c>
+      <c r="I23" s="5">
+        <v>6</v>
+      </c>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J21"/>
